--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="浅水湾道3号 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,42 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -793,7 +669,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1999-06-10</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -839,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -885,7 +761,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -931,7 +807,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -977,7 +853,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-12-15</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1023,7 +899,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1069,7 +945,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-12-15</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1115,7 +991,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1311,7 +1187,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-10-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1407,7 +1283,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1999-03-10</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1553,7 +1429,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-03</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1649,7 +1525,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-24</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1695,7 +1571,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-24</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1741,7 +1617,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1787,7 +1663,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-11</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1833,7 +1709,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-24</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1879,7 +1755,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1975,7 +1851,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2021,7 +1897,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2067,7 +1943,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-03</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2113,7 +1989,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-06</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2159,7 +2035,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-06</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2205,7 +2081,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-10</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2251,7 +2127,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2297,7 +2173,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2343,7 +2219,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2389,7 +2265,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-06</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2435,7 +2311,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2481,7 +2357,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-04</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2577,7 +2453,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1997-07-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2649,598 +2525,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No.3 Repulse Bay Road - 浅水湾道3号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3510呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 3250呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1709呎 (4+房)
-$5,157万
-$30,176/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1632呎 (4+房)
-$2,830万
-$17,341/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1709呎 (4+房)
-$5,193万
-$30,386/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1632呎 (4+房)
-$5,654万
-$34,645/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$5,750万
-$33,027/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1682呎 (4+房)
-$4,987万
-$29,650/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$5,168万
-$29,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1682呎 (4+房)
-$4,987万
-$29,650/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1682呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$5,854万
-$33,627/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1682呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$2,359万
-$13,551/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-$5,200万
-$31,119/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$5,180万
-$29,753/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-$4,700万
-$28,127/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1741呎 (4+房)
-$5,200万
-$29,868/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-$5,400万
-$32,316/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1796呎 (4+房)
-$4,800万
-$26,726/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1671呎 (4+房)
-$4,670万
-$27,947/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$4,800万
-$27,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1664呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$4,780万
-$27,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1664呎 (4+房)
-$5,020万
-$30,168/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$5,331万
-$30,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1664呎 (4+房)
-$5,000万
-$30,048/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$4,760万
-$27,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1664呎 (4+房)
-$4,850万
-$29,147/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$4,760万
-$27,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1659呎 (4+房)
-$4,750万
-$28,632/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-$4,860万
-$28,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1659呎 (4+房)
-$4,750万
-$28,632/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1659呎 (4+房)
-$4,700万
-$28,330/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1734呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1659呎 (4+房)
-$4,720万
-$28,451/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="浅水湾道3号" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +211,54 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +635,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2525,4 +2686,598 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>浅水湾道3号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3510呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 3250呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1709呎 (4+房)
+$5157万
+$30,176/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1632呎 (4+房)
+$2830万
+$17,341/呎
+(99年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1709呎 (4+房)
+$5193万
+$30,386/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1632呎 (4+房)
+$5654万
+$34,645/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$5750万
+$33,027/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1682呎 (4+房)
+$4987万
+$29,650/呎
+(97年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$5168万
+$29,685/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1682呎 (4+房)
+$4987万
+$29,650/呎
+(97年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1682呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$5854万
+$33,627/呎
+(97年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1682呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$2359万
+$13,551/呎
+(99年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+$5200万
+$31,119/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$5180万
+$29,753/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+$4700万
+$28,127/呎
+(97年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1741呎 (4+房)
+$5200万
+$29,868/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+$5400万
+$32,316/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1796呎 (4+房)
+$4800万
+$26,726/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1671呎 (4+房)
+$4670万
+$27,947/呎
+(97年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$4800万
+$27,682/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1664呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$4780万
+$27,566/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1664呎 (4+房)
+$5020万
+$30,168/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$5331万
+$30,744/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1664呎 (4+房)
+$5000万
+$30,048/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$4760万
+$27,451/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1664呎 (4+房)
+$4850万
+$29,147/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$4760万
+$27,451/呎
+(97年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1659呎 (4+房)
+$4750万
+$28,632/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+$4860万
+$28,028/呎
+(97年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1659呎 (4+房)
+$4750万
+$28,632/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1659呎 (4+房)
+$4700万
+$28,330/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1734呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1659呎 (4+房)
+$4720万
+$28,451/呎
+(97年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -635,7 +635,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -638,6 +638,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -695,6 +699,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -745,6 +769,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -795,6 +839,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -841,6 +905,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -887,6 +971,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -933,6 +1037,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -979,6 +1103,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1025,6 +1169,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1071,6 +1235,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1117,6 +1301,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1163,6 +1367,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1213,6 +1437,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1263,6 +1507,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1313,6 +1577,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1359,6 +1643,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1409,6 +1713,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1455,6 +1779,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1505,6 +1849,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1555,6 +1919,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1601,6 +1985,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1651,6 +2055,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1697,6 +2121,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1743,6 +2187,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1789,6 +2253,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1835,6 +2319,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1881,6 +2385,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1927,6 +2451,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1977,6 +2521,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2023,6 +2587,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2069,6 +2653,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2115,6 +2719,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2161,6 +2785,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2207,6 +2851,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2253,6 +2917,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2299,6 +2983,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2345,6 +3049,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2391,6 +3115,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2437,6 +3181,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2483,6 +3247,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2529,6 +3313,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2579,6 +3383,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2625,6 +3449,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2675,13 +3519,33 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2824,7 +3688,7 @@
           <t>A | 1709呎 (4+房)
 $5157万
 $30,176/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -2832,7 +3696,7 @@
           <t>B | 1632呎 (4+房)
 $2830万
 $17,341/呎
-(99年-06月)</t>
+(99年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +3711,7 @@
           <t>A | 1709呎 (4+房)
 $5193万
 $30,386/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -2855,7 +3719,7 @@
           <t>B | 1632呎 (4+房)
 $5654万
 $34,645/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -2870,7 +3734,7 @@
           <t>A | 1741呎 (4+房)
 $5750万
 $33,027/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -2878,7 +3742,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月)</t>
+(97年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -2893,7 +3757,7 @@
           <t>A | 1741呎 (4+房)
 $5168万
 $29,685/呎
-(97年-07月)</t>
+(97年-07月-18日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -2901,7 +3765,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月)</t>
+(97年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -2939,7 +3803,7 @@
           <t>A | 1741呎 (4+房)
 $5854万
 $33,627/呎
-(97年-10月)</t>
+(97年-10月-21日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2962,7 +3826,7 @@
           <t>A | 1741呎 (4+房)
 $2359万
 $13,551/呎
-(99年-03月)</t>
+(99年-03月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3016,7 +3880,7 @@
           <t>B | 1671呎 (4+房)
 $5200万
 $31,119/呎
-(97年-07月)</t>
+(97年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3895,7 @@
           <t>A | 1741呎 (4+房)
 $5180万
 $29,753/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -3039,7 +3903,7 @@
           <t>B | 1671呎 (4+房)
 $4700万
 $28,127/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3918,7 @@
           <t>A | 1741呎 (4+房)
 $5200万
 $29,868/呎
-(97年-07月)</t>
+(97年-07月-11日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -3062,7 +3926,7 @@
           <t>B | 1671呎 (4+房)
 $5400万
 $32,316/呎
-(97年-07月)</t>
+(97年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3941,7 @@
           <t>A | 1796呎 (4+房)
 $4800万
 $26,726/呎
-(97年-06月)</t>
+(97年-06月-25日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -3085,7 +3949,7 @@
           <t>B | 1671呎 (4+房)
 $4670万
 $27,947/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3964,7 @@
           <t>A | 1734呎 (4+房)
 $4800万
 $27,682/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3123,7 +3987,7 @@
           <t>A | 1734呎 (4+房)
 $4780万
 $27,566/呎
-(97年-07月)</t>
+(97年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -3131,7 +3995,7 @@
           <t>B | 1664呎 (4+房)
 $5020万
 $30,168/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -3146,7 +4010,7 @@
           <t>A | 1734呎 (4+房)
 $5331万
 $30,744/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -3154,7 +4018,7 @@
           <t>B | 1664呎 (4+房)
 $5000万
 $30,048/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -3169,7 +4033,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -3177,7 +4041,7 @@
           <t>B | 1664呎 (4+房)
 $4850万
 $29,147/呎
-(97年-07月)</t>
+(97年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -3192,7 +4056,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -3200,7 +4064,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月)</t>
+(97年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -3215,7 +4079,7 @@
           <t>A | 1734呎 (4+房)
 $4860万
 $28,028/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -3223,7 +4087,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -3246,7 +4110,7 @@
           <t>B | 1659呎 (4+房)
 $4700万
 $28,330/呎
-(97年-07月)</t>
+(97年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -3269,7 +4133,7 @@
           <t>B | 1659呎 (4+房)
 $4720万
 $28,451/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -3688,7 +3688,7 @@
           <t>A | 1709呎 (4+房)
 $5157万
 $30,176/呎
-(97年-06月-26日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -3696,7 +3696,7 @@
           <t>B | 1632呎 (4+房)
 $2830万
 $17,341/呎
-(99年-06月-10日)</t>
+(99年-06月)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
           <t>A | 1709呎 (4+房)
 $5193万
 $30,386/呎
-(97年-06月-26日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -3719,7 +3719,7 @@
           <t>B | 1632呎 (4+房)
 $5654万
 $34,645/呎
-(97年-07月-07日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
           <t>A | 1741呎 (4+房)
 $5750万
 $33,027/呎
-(97年-07月-07日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -3742,7 +3742,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月-15日)</t>
+(97年-12月)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
           <t>A | 1741呎 (4+房)
 $5168万
 $29,685/呎
-(97年-07月-18日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -3765,7 +3765,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月-15日)</t>
+(97年-12月)</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
           <t>A | 1741呎 (4+房)
 $5854万
 $33,627/呎
-(97年-10月-21日)</t>
+(97年-10月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3826,7 +3826,7 @@
           <t>A | 1741呎 (4+房)
 $2359万
 $13,551/呎
-(99年-03月-10日)</t>
+(99年-03月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3880,7 +3880,7 @@
           <t>B | 1671呎 (4+房)
 $5200万
 $31,119/呎
-(97年-07月-03日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
           <t>A | 1741呎 (4+房)
 $5180万
 $29,753/呎
-(97年-06月-24日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -3903,7 +3903,7 @@
           <t>B | 1671呎 (4+房)
 $4700万
 $28,127/呎
-(97年-06月-24日)</t>
+(97年-06月)</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
           <t>A | 1741呎 (4+房)
 $5200万
 $29,868/呎
-(97年-07月-11日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -3926,7 +3926,7 @@
           <t>B | 1671呎 (4+房)
 $5400万
 $32,316/呎
-(97年-07月-11日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
           <t>A | 1796呎 (4+房)
 $4800万
 $26,726/呎
-(97年-06月-25日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -3949,7 +3949,7 @@
           <t>B | 1671呎 (4+房)
 $4670万
 $27,947/呎
-(97年-06月-24日)</t>
+(97年-06月)</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
           <t>A | 1734呎 (4+房)
 $4800万
 $27,682/呎
-(97年-06月-26日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3987,7 +3987,7 @@
           <t>A | 1734呎 (4+房)
 $4780万
 $27,566/呎
-(97年-07月-03日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -3995,7 +3995,7 @@
           <t>B | 1664呎 (4+房)
 $5020万
 $30,168/呎
-(97年-07月-07日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
           <t>A | 1734呎 (4+房)
 $5331万
 $30,744/呎
-(97年-07月-06日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -4018,7 +4018,7 @@
           <t>B | 1664呎 (4+房)
 $5000万
 $30,048/呎
-(97年-07月-06日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月-26日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -4041,7 +4041,7 @@
           <t>B | 1664呎 (4+房)
 $4850万
 $29,147/呎
-(97年-07月-10日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月-26日)</t>
+(97年-06月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -4064,7 +4064,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月-16日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
           <t>A | 1734呎 (4+房)
 $4860万
 $28,028/呎
-(97年-07月-06日)</t>
+(97年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -4087,7 +4087,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月-06日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
           <t>B | 1659呎 (4+房)
 $4700万
 $28,330/呎
-(97年-07月-04日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
           <t>B | 1659呎 (4+房)
 $4720万
 $28,451/呎
-(97年-07月-06日)</t>
+(97年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -3688,7 +3688,7 @@
           <t>A | 1709呎 (4+房)
 $5157万
 $30,176/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -3696,7 +3696,7 @@
           <t>B | 1632呎 (4+房)
 $2830万
 $17,341/呎
-(99年-06月)</t>
+(99年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
           <t>A | 1709呎 (4+房)
 $5193万
 $30,386/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -3719,7 +3719,7 @@
           <t>B | 1632呎 (4+房)
 $5654万
 $34,645/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
           <t>A | 1741呎 (4+房)
 $5750万
 $33,027/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -3742,7 +3742,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月)</t>
+(97年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
           <t>A | 1741呎 (4+房)
 $5168万
 $29,685/呎
-(97年-07月)</t>
+(97年-07月-18日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -3765,7 +3765,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月)</t>
+(97年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
           <t>A | 1741呎 (4+房)
 $5854万
 $33,627/呎
-(97年-10月)</t>
+(97年-10月-21日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3826,7 +3826,7 @@
           <t>A | 1741呎 (4+房)
 $2359万
 $13,551/呎
-(99年-03月)</t>
+(99年-03月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3880,7 +3880,7 @@
           <t>B | 1671呎 (4+房)
 $5200万
 $31,119/呎
-(97年-07月)</t>
+(97年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
           <t>A | 1741呎 (4+房)
 $5180万
 $29,753/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -3903,7 +3903,7 @@
           <t>B | 1671呎 (4+房)
 $4700万
 $28,127/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
           <t>A | 1741呎 (4+房)
 $5200万
 $29,868/呎
-(97年-07月)</t>
+(97年-07月-11日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -3926,7 +3926,7 @@
           <t>B | 1671呎 (4+房)
 $5400万
 $32,316/呎
-(97年-07月)</t>
+(97年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
           <t>A | 1796呎 (4+房)
 $4800万
 $26,726/呎
-(97年-06月)</t>
+(97年-06月-25日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -3949,7 +3949,7 @@
           <t>B | 1671呎 (4+房)
 $4670万
 $27,947/呎
-(97年-06月)</t>
+(97年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
           <t>A | 1734呎 (4+房)
 $4800万
 $27,682/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3987,7 +3987,7 @@
           <t>A | 1734呎 (4+房)
 $4780万
 $27,566/呎
-(97年-07月)</t>
+(97年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -3995,7 +3995,7 @@
           <t>B | 1664呎 (4+房)
 $5020万
 $30,168/呎
-(97年-07月)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
           <t>A | 1734呎 (4+房)
 $5331万
 $30,744/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -4018,7 +4018,7 @@
           <t>B | 1664呎 (4+房)
 $5000万
 $30,048/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -4041,7 +4041,7 @@
           <t>B | 1664呎 (4+房)
 $4850万
 $29,147/呎
-(97年-07月)</t>
+(97年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -4064,7 +4064,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月)</t>
+(97年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
           <t>A | 1734呎 (4+房)
 $4860万
 $28,028/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -4087,7 +4087,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
           <t>B | 1659呎 (4+房)
 $4700万
 $28,330/呎
-(97年-07月)</t>
+(97年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
           <t>B | 1659呎 (4+房)
 $4720万
 $28,451/呎
-(97年-07月)</t>
+(97年-07月-06日)</t>
         </is>
       </c>
     </row>
